--- a/Data_Timbulan_Sampah/Data_Timbulan_Sampah_SIPSN_KLHK_2021.xlsx
+++ b/Data_Timbulan_Sampah/Data_Timbulan_Sampah_SIPSN_KLHK_2021.xlsx
@@ -201,8 +201,8 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <cols>
     <col min="1" max="1" width="6.75" customWidth="1"/>
-    <col min="2" max="2" width="18.900000000000002" customWidth="1"/>
-    <col min="3" max="3" width="27" customWidth="1"/>
+    <col min="2" max="2" width="35.1" customWidth="1"/>
+    <col min="3" max="3" width="40.5" customWidth="1"/>
     <col min="4" max="4" width="36.45" customWidth="1"/>
     <col min="5" max="5" width="37.800000000000004" customWidth="1"/>
   </cols>
@@ -451,6 +451,4668 @@
         <v>82781.59</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B13">
+        <is>
+          <t xml:space="preserve">Sumatera Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C13">
+        <is>
+          <t xml:space="preserve">Kab. Deli Serdang</t>
+        </is>
+      </c>
+      <c r="D13" s="64">
+        <v>1118.16</v>
+      </c>
+      <c r="E13" s="64">
+        <v>408129.86</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B14">
+        <is>
+          <t xml:space="preserve">Sumatera Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C14">
+        <is>
+          <t xml:space="preserve">Kab. Simalungun</t>
+        </is>
+      </c>
+      <c r="D14" s="66">
+        <v>519.06</v>
+      </c>
+      <c r="E14" s="64">
+        <v>189456.90</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B15">
+        <is>
+          <t xml:space="preserve">Sumatera Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C15">
+        <is>
+          <t xml:space="preserve">Kab. Asahan</t>
+        </is>
+      </c>
+      <c r="D15" s="66">
+        <v>466.58</v>
+      </c>
+      <c r="E15" s="64">
+        <v>170300.09</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B16">
+        <is>
+          <t xml:space="preserve">Sumatera Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C16">
+        <is>
+          <t xml:space="preserve">Kab. Labuhanbatu</t>
+        </is>
+      </c>
+      <c r="D16" s="66">
+        <v>249.99</v>
+      </c>
+      <c r="E16" s="64">
+        <v>91246.72</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B17">
+        <is>
+          <t xml:space="preserve">Sumatera Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C17">
+        <is>
+          <t xml:space="preserve">Kab. Toba</t>
+        </is>
+      </c>
+      <c r="D17" s="66">
+        <v>108.24</v>
+      </c>
+      <c r="E17" s="64">
+        <v>39509.06</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B18">
+        <is>
+          <t xml:space="preserve">Sumatera Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C18">
+        <is>
+          <t xml:space="preserve">Kab. Samosir</t>
+        </is>
+      </c>
+      <c r="D18" s="66">
+        <v>89.50</v>
+      </c>
+      <c r="E18" s="64">
+        <v>32668.38</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B19">
+        <is>
+          <t xml:space="preserve">Sumatera Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C19">
+        <is>
+          <t xml:space="preserve">Kota Medan</t>
+        </is>
+      </c>
+      <c r="D19" s="64">
+        <v>1767.16</v>
+      </c>
+      <c r="E19" s="64">
+        <v>645012.56</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B20">
+        <is>
+          <t xml:space="preserve">Sumatera Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C20">
+        <is>
+          <t xml:space="preserve">Kota Pematangsiantar</t>
+        </is>
+      </c>
+      <c r="D20" s="66">
+        <v>233.02</v>
+      </c>
+      <c r="E20" s="64">
+        <v>85052.00</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B21">
+        <is>
+          <t xml:space="preserve">Sumatera Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C21">
+        <is>
+          <t xml:space="preserve">Kota Tebing Tinggi</t>
+        </is>
+      </c>
+      <c r="D21" s="66">
+        <v>123.50</v>
+      </c>
+      <c r="E21" s="64">
+        <v>45077.61</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B22">
+        <is>
+          <t xml:space="preserve">Sumatera Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C22">
+        <is>
+          <t xml:space="preserve">Kab. Pesisir Selatan</t>
+        </is>
+      </c>
+      <c r="D22" s="66">
+        <v>151.33</v>
+      </c>
+      <c r="E22" s="64">
+        <v>55233.77</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B23">
+        <is>
+          <t xml:space="preserve">Sumatera Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C23">
+        <is>
+          <t xml:space="preserve">Kab. Tanah Datar</t>
+        </is>
+      </c>
+      <c r="D23" s="66">
+        <v>128.24</v>
+      </c>
+      <c r="E23" s="64">
+        <v>46806.83</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B24">
+        <is>
+          <t xml:space="preserve">Sumatera Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C24">
+        <is>
+          <t xml:space="preserve">Kab. Agam</t>
+        </is>
+      </c>
+      <c r="D24" s="66">
+        <v>214.83</v>
+      </c>
+      <c r="E24" s="64">
+        <v>78412.95</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B25">
+        <is>
+          <t xml:space="preserve">Sumatera Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C25">
+        <is>
+          <t xml:space="preserve">Kab. Lima Puluh Kota</t>
+        </is>
+      </c>
+      <c r="D25" s="66">
+        <v>154.23</v>
+      </c>
+      <c r="E25" s="64">
+        <v>56295.41</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B26">
+        <is>
+          <t xml:space="preserve">Sumatera Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C26">
+        <is>
+          <t xml:space="preserve">Kab. Pasaman</t>
+        </is>
+      </c>
+      <c r="D26" s="66">
+        <v>121.24</v>
+      </c>
+      <c r="E26" s="64">
+        <v>44253.04</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B27">
+        <is>
+          <t xml:space="preserve">Sumatera Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C27">
+        <is>
+          <t xml:space="preserve">Kab. Dharmasraya</t>
+        </is>
+      </c>
+      <c r="D27" s="66">
+        <v>102.50</v>
+      </c>
+      <c r="E27" s="64">
+        <v>37411.62</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B28">
+        <is>
+          <t xml:space="preserve">Sumatera Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C28">
+        <is>
+          <t xml:space="preserve">Kab. Solok Selatan</t>
+        </is>
+      </c>
+      <c r="D28" s="66">
+        <v>73.94</v>
+      </c>
+      <c r="E28" s="64">
+        <v>26988.10</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B29">
+        <is>
+          <t xml:space="preserve">Sumatera Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C29">
+        <is>
+          <t xml:space="preserve">Kota Solok</t>
+        </is>
+      </c>
+      <c r="D29" s="66">
+        <v>53.87</v>
+      </c>
+      <c r="E29" s="64">
+        <v>19663.02</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B30">
+        <is>
+          <t xml:space="preserve">Sumatera Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C30">
+        <is>
+          <t xml:space="preserve">Kota Sawahlunto</t>
+        </is>
+      </c>
+      <c r="D30" s="66">
+        <v>18.75</v>
+      </c>
+      <c r="E30" s="64">
+        <v>6843.52</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B31">
+        <is>
+          <t xml:space="preserve">Sumatera Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C31">
+        <is>
+          <t xml:space="preserve">Kota Padang Panjang</t>
+        </is>
+      </c>
+      <c r="D31" s="66">
+        <v>48.00</v>
+      </c>
+      <c r="E31" s="64">
+        <v>17519.42</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B32">
+        <is>
+          <t xml:space="preserve">Sumatera Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C32">
+        <is>
+          <t xml:space="preserve">Kota Payakumbuh</t>
+        </is>
+      </c>
+      <c r="D32" s="66">
+        <v>98.80</v>
+      </c>
+      <c r="E32" s="64">
+        <v>36063.06</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B33">
+        <is>
+          <t xml:space="preserve">Riau</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C33">
+        <is>
+          <t xml:space="preserve">Kab. Indragiri Hilir</t>
+        </is>
+      </c>
+      <c r="D33" s="66">
+        <v>460.62</v>
+      </c>
+      <c r="E33" s="64">
+        <v>168125.39</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B34">
+        <is>
+          <t xml:space="preserve">Riau</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C34">
+        <is>
+          <t xml:space="preserve">Kab. Siak</t>
+        </is>
+      </c>
+      <c r="D34" s="66">
+        <v>191.07</v>
+      </c>
+      <c r="E34" s="64">
+        <v>69739.82</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B35">
+        <is>
+          <t xml:space="preserve">Riau</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C35">
+        <is>
+          <t xml:space="preserve">Kota Pekanbaru</t>
+        </is>
+      </c>
+      <c r="D35" s="66">
+        <v>967.49</v>
+      </c>
+      <c r="E35" s="64">
+        <v>353133.89</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B36">
+        <is>
+          <t xml:space="preserve">Riau</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C36">
+        <is>
+          <t xml:space="preserve">Kota Dumai</t>
+        </is>
+      </c>
+      <c r="D36" s="66">
+        <v>161.73</v>
+      </c>
+      <c r="E36" s="64">
+        <v>59029.99</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B37">
+        <is>
+          <t xml:space="preserve">Jambi</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C37">
+        <is>
+          <t xml:space="preserve">Kab. Merangin</t>
+        </is>
+      </c>
+      <c r="D37" s="66">
+        <v>198.75</v>
+      </c>
+      <c r="E37" s="64">
+        <v>72545.03</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B38">
+        <is>
+          <t xml:space="preserve">Jambi</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C38">
+        <is>
+          <t xml:space="preserve">Kab. Bungo</t>
+        </is>
+      </c>
+      <c r="D38" s="66">
+        <v>155.40</v>
+      </c>
+      <c r="E38" s="64">
+        <v>56722.46</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B39">
+        <is>
+          <t xml:space="preserve">Jambi</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C39">
+        <is>
+          <t xml:space="preserve">Kota Jambi</t>
+        </is>
+      </c>
+      <c r="D39" s="66">
+        <v>433.17</v>
+      </c>
+      <c r="E39" s="64">
+        <v>158106.98</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B40">
+        <is>
+          <t xml:space="preserve">Sumatera Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C40">
+        <is>
+          <t xml:space="preserve">Kab. Muara Enim</t>
+        </is>
+      </c>
+      <c r="D40" s="66">
+        <v>232.42</v>
+      </c>
+      <c r="E40" s="64">
+        <v>84833.74</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B41">
+        <is>
+          <t xml:space="preserve">Sumatera Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C41">
+        <is>
+          <t xml:space="preserve">Kab. Lahat</t>
+        </is>
+      </c>
+      <c r="D41" s="66">
+        <v>307.84</v>
+      </c>
+      <c r="E41" s="64">
+        <v>112361.75</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B42">
+        <is>
+          <t xml:space="preserve">Sumatera Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C42">
+        <is>
+          <t xml:space="preserve">Kab. Musi Banyuasin</t>
+        </is>
+      </c>
+      <c r="D42" s="66">
+        <v>248.88</v>
+      </c>
+      <c r="E42" s="64">
+        <v>90842.08</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B43">
+        <is>
+          <t xml:space="preserve">Sumatera Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C43">
+        <is>
+          <t xml:space="preserve">Kab. Ogan Komering Ulu Timur</t>
+        </is>
+      </c>
+      <c r="D43" s="66">
+        <v>280.08</v>
+      </c>
+      <c r="E43" s="64">
+        <v>102228.32</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B44">
+        <is>
+          <t xml:space="preserve">Sumatera Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C44">
+        <is>
+          <t xml:space="preserve">Kota Palembang</t>
+        </is>
+      </c>
+      <c r="D44" s="64">
+        <v>1180.25</v>
+      </c>
+      <c r="E44" s="64">
+        <v>430791.65</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B45">
+        <is>
+          <t xml:space="preserve">Sumatera Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C45">
+        <is>
+          <t xml:space="preserve">Kota Prabumulih</t>
+        </is>
+      </c>
+      <c r="D45" s="66">
+        <v>97.06</v>
+      </c>
+      <c r="E45" s="64">
+        <v>35426.54</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B46">
+        <is>
+          <t xml:space="preserve">Bengkulu</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C46">
+        <is>
+          <t xml:space="preserve">Kab. Seluma</t>
+        </is>
+      </c>
+      <c r="D46" s="66">
+        <v>106.76</v>
+      </c>
+      <c r="E46" s="64">
+        <v>38966.12</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B47">
+        <is>
+          <t xml:space="preserve">Lampung</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C47">
+        <is>
+          <t xml:space="preserve">Kab. Tanggamus</t>
+        </is>
+      </c>
+      <c r="D47" s="66">
+        <v>245.98</v>
+      </c>
+      <c r="E47" s="64">
+        <v>89783.28</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B48">
+        <is>
+          <t xml:space="preserve">Lampung</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C48">
+        <is>
+          <t xml:space="preserve">Kab. Way Kanan</t>
+        </is>
+      </c>
+      <c r="D48" s="66">
+        <v>191.88</v>
+      </c>
+      <c r="E48" s="64">
+        <v>70036.49</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B49">
+        <is>
+          <t xml:space="preserve">Lampung</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C49">
+        <is>
+          <t xml:space="preserve">Kab. Pringsewu</t>
+        </is>
+      </c>
+      <c r="D49" s="66">
+        <v>162.73</v>
+      </c>
+      <c r="E49" s="64">
+        <v>59396.16</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B50">
+        <is>
+          <t xml:space="preserve">Lampung</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C50">
+        <is>
+          <t xml:space="preserve">Kota Bandar Lampung</t>
+        </is>
+      </c>
+      <c r="D50" s="66">
+        <v>770.22</v>
+      </c>
+      <c r="E50" s="64">
+        <v>281129.15</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B51">
+        <is>
+          <t xml:space="preserve">Kepulauan Bangka Belitung</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C51">
+        <is>
+          <t xml:space="preserve">Kab. Bangka</t>
+        </is>
+      </c>
+      <c r="D51" s="66">
+        <v>130.51</v>
+      </c>
+      <c r="E51" s="64">
+        <v>47634.69</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B52">
+        <is>
+          <t xml:space="preserve">Kepulauan Bangka Belitung</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C52">
+        <is>
+          <t xml:space="preserve">Kab. Belitung</t>
+        </is>
+      </c>
+      <c r="D52" s="66">
+        <v>72.69</v>
+      </c>
+      <c r="E52" s="64">
+        <v>26533.31</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B53">
+        <is>
+          <t xml:space="preserve">Kepulauan Bangka Belitung</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C53">
+        <is>
+          <t xml:space="preserve">Kab. Bangka Selatan</t>
+        </is>
+      </c>
+      <c r="D53" s="66">
+        <v>80.13</v>
+      </c>
+      <c r="E53" s="64">
+        <v>29247.45</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B54">
+        <is>
+          <t xml:space="preserve">Kepulauan Bangka Belitung</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C54">
+        <is>
+          <t xml:space="preserve">Kab. Bangka Tengah</t>
+        </is>
+      </c>
+      <c r="D54" s="66">
+        <v>81.17</v>
+      </c>
+      <c r="E54" s="64">
+        <v>29627.05</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B55">
+        <is>
+          <t xml:space="preserve">Kepulauan Bangka Belitung</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C55">
+        <is>
+          <t xml:space="preserve">Kota Pangkal Pinang</t>
+        </is>
+      </c>
+      <c r="D55" s="66">
+        <v>160.00</v>
+      </c>
+      <c r="E55" s="64">
+        <v>58399.38</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B56">
+        <is>
+          <t xml:space="preserve">Kepulauan Riau</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C56">
+        <is>
+          <t xml:space="preserve">Kab. Bintan</t>
+        </is>
+      </c>
+      <c r="D56" s="66">
+        <v>55.69</v>
+      </c>
+      <c r="E56" s="64">
+        <v>20326.42</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B57">
+        <is>
+          <t xml:space="preserve">Kepulauan Riau</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C57">
+        <is>
+          <t xml:space="preserve">Kab. Karimun</t>
+        </is>
+      </c>
+      <c r="D57" s="66">
+        <v>181.62</v>
+      </c>
+      <c r="E57" s="64">
+        <v>66289.99</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B58">
+        <is>
+          <t xml:space="preserve">Kepulauan Riau</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C58">
+        <is>
+          <t xml:space="preserve">Kota Tanjung Pinang</t>
+        </is>
+      </c>
+      <c r="D58" s="66">
+        <v>151.69</v>
+      </c>
+      <c r="E58" s="64">
+        <v>55366.32</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B59">
+        <is>
+          <t xml:space="preserve">DKI Jakarta</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C59">
+        <is>
+          <t xml:space="preserve">Kab. Adm. Kep. Seribu</t>
+        </is>
+      </c>
+      <c r="D59" s="66">
+        <v>17.62</v>
+      </c>
+      <c r="E59" s="64">
+        <v>6429.48</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B60">
+        <is>
+          <t xml:space="preserve">DKI Jakarta</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C60">
+        <is>
+          <t xml:space="preserve">Kota Adm. Jakarta Pusat</t>
+        </is>
+      </c>
+      <c r="D60" s="66">
+        <v>847.39</v>
+      </c>
+      <c r="E60" s="64">
+        <v>309298.18</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B61">
+        <is>
+          <t xml:space="preserve">DKI Jakarta</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C61">
+        <is>
+          <t xml:space="preserve">Kota Adm. Jakarta Utara</t>
+        </is>
+      </c>
+      <c r="D61" s="64">
+        <v>1354.67</v>
+      </c>
+      <c r="E61" s="64">
+        <v>494454.86</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B62">
+        <is>
+          <t xml:space="preserve">DKI Jakarta</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C62">
+        <is>
+          <t xml:space="preserve">Kota Adm. Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="D62" s="64">
+        <v>1937.54</v>
+      </c>
+      <c r="E62" s="64">
+        <v>707201.35</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B63">
+        <is>
+          <t xml:space="preserve">DKI Jakarta</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C63">
+        <is>
+          <t xml:space="preserve">Kota Adm. Jakarta Timur</t>
+        </is>
+      </c>
+      <c r="D63" s="64">
+        <v>2293.04</v>
+      </c>
+      <c r="E63" s="64">
+        <v>836961.37</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B64">
+        <is>
+          <t xml:space="preserve">Jawa Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C64">
+        <is>
+          <t xml:space="preserve">Kab. Bandung</t>
+        </is>
+      </c>
+      <c r="D64" s="64">
+        <v>1268.33</v>
+      </c>
+      <c r="E64" s="64">
+        <v>462939.17</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B65">
+        <is>
+          <t xml:space="preserve">Jawa Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C65">
+        <is>
+          <t xml:space="preserve">Kab. Garut</t>
+        </is>
+      </c>
+      <c r="D65" s="64">
+        <v>1120.06</v>
+      </c>
+      <c r="E65" s="64">
+        <v>408821.79</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B66">
+        <is>
+          <t xml:space="preserve">Jawa Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C66">
+        <is>
+          <t xml:space="preserve">Kab. Ciamis</t>
+        </is>
+      </c>
+      <c r="D66" s="66">
+        <v>572.10</v>
+      </c>
+      <c r="E66" s="64">
+        <v>208818.25</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B67">
+        <is>
+          <t xml:space="preserve">Jawa Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C67">
+        <is>
+          <t xml:space="preserve">Kab. Cirebon</t>
+        </is>
+      </c>
+      <c r="D67" s="64">
+        <v>1237.12</v>
+      </c>
+      <c r="E67" s="64">
+        <v>451549.60</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B68">
+        <is>
+          <t xml:space="preserve">Jawa Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C68">
+        <is>
+          <t xml:space="preserve">Kab. Sumedang</t>
+        </is>
+      </c>
+      <c r="D68" s="66">
+        <v>442.36</v>
+      </c>
+      <c r="E68" s="64">
+        <v>161462.89</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B69">
+        <is>
+          <t xml:space="preserve">Jawa Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C69">
+        <is>
+          <t xml:space="preserve">Kab. Indramayu</t>
+        </is>
+      </c>
+      <c r="D69" s="64">
+        <v>1102.62</v>
+      </c>
+      <c r="E69" s="64">
+        <v>402455.25</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B70">
+        <is>
+          <t xml:space="preserve">Jawa Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C70">
+        <is>
+          <t xml:space="preserve">Kota Bogor</t>
+        </is>
+      </c>
+      <c r="D70" s="66">
+        <v>673.76</v>
+      </c>
+      <c r="E70" s="64">
+        <v>245922.33</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B71">
+        <is>
+          <t xml:space="preserve">Jawa Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C71">
+        <is>
+          <t xml:space="preserve">Kota Sukabumi</t>
+        </is>
+      </c>
+      <c r="D71" s="66">
+        <v>180.26</v>
+      </c>
+      <c r="E71" s="64">
+        <v>65795.65</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B72">
+        <is>
+          <t xml:space="preserve">Jawa Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C72">
+        <is>
+          <t xml:space="preserve">Kota Bandung</t>
+        </is>
+      </c>
+      <c r="D72" s="64">
+        <v>1592.55</v>
+      </c>
+      <c r="E72" s="64">
+        <v>581280.03</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B73">
+        <is>
+          <t xml:space="preserve">Jawa Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C73">
+        <is>
+          <t xml:space="preserve">Kota Cirebon</t>
+        </is>
+      </c>
+      <c r="D73" s="66">
+        <v>204.47</v>
+      </c>
+      <c r="E73" s="64">
+        <v>74631.55</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B74">
+        <is>
+          <t xml:space="preserve">Jawa Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C74">
+        <is>
+          <t xml:space="preserve">Kota Bekasi</t>
+        </is>
+      </c>
+      <c r="D74" s="64">
+        <v>2375.99</v>
+      </c>
+      <c r="E74" s="64">
+        <v>867236.75</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B75">
+        <is>
+          <t xml:space="preserve">Jawa Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C75">
+        <is>
+          <t xml:space="preserve">Kota Depok</t>
+        </is>
+      </c>
+      <c r="D75" s="64">
+        <v>1314.14</v>
+      </c>
+      <c r="E75" s="64">
+        <v>479660.75</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B76">
+        <is>
+          <t xml:space="preserve">Jawa Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C76">
+        <is>
+          <t xml:space="preserve">Kota Cimahi</t>
+        </is>
+      </c>
+      <c r="D76" s="66">
+        <v>274.77</v>
+      </c>
+      <c r="E76" s="64">
+        <v>100289.42</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B77">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C77">
+        <is>
+          <t xml:space="preserve">Kab. Cilacap</t>
+        </is>
+      </c>
+      <c r="D77" s="66">
+        <v>943.59</v>
+      </c>
+      <c r="E77" s="64">
+        <v>344409.04</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B78">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C78">
+        <is>
+          <t xml:space="preserve">Kab. Banyumas</t>
+        </is>
+      </c>
+      <c r="D78" s="66">
+        <v>535.23</v>
+      </c>
+      <c r="E78" s="64">
+        <v>195357.75</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B79">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C79">
+        <is>
+          <t xml:space="preserve">Kab. Purbalingga</t>
+        </is>
+      </c>
+      <c r="D79" s="66">
+        <v>505.71</v>
+      </c>
+      <c r="E79" s="64">
+        <v>184585.06</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B80">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C80">
+        <is>
+          <t xml:space="preserve">Kab. Purworejo</t>
+        </is>
+      </c>
+      <c r="D80" s="66">
+        <v>288.82</v>
+      </c>
+      <c r="E80" s="64">
+        <v>105420.18</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B81">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C81">
+        <is>
+          <t xml:space="preserve">Kab. Wonosobo</t>
+        </is>
+      </c>
+      <c r="D81" s="66">
+        <v>363.00</v>
+      </c>
+      <c r="E81" s="64">
+        <v>132496.46</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B82">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C82">
+        <is>
+          <t xml:space="preserve">Kab. Magelang</t>
+        </is>
+      </c>
+      <c r="D82" s="66">
+        <v>681.65</v>
+      </c>
+      <c r="E82" s="64">
+        <v>248800.43</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B83">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C83">
+        <is>
+          <t xml:space="preserve">Kab. Boyolali</t>
+        </is>
+      </c>
+      <c r="D83" s="66">
+        <v>290.85</v>
+      </c>
+      <c r="E83" s="64">
+        <v>106159.34</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B84">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C84">
+        <is>
+          <t xml:space="preserve">Kab. Klaten</t>
+        </is>
+      </c>
+      <c r="D84" s="66">
+        <v>590.30</v>
+      </c>
+      <c r="E84" s="64">
+        <v>215458.83</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B85">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C85">
+        <is>
+          <t xml:space="preserve">Kab. Sukoharjo</t>
+        </is>
+      </c>
+      <c r="D85" s="66">
+        <v>359.45</v>
+      </c>
+      <c r="E85" s="64">
+        <v>131200.56</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B86">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C86">
+        <is>
+          <t xml:space="preserve">Kab. Wonogiri</t>
+        </is>
+      </c>
+      <c r="D86" s="66">
+        <v>439.37</v>
+      </c>
+      <c r="E86" s="64">
+        <v>160369.61</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B87">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C87">
+        <is>
+          <t xml:space="preserve">Kab. Karanganyar</t>
+        </is>
+      </c>
+      <c r="D87" s="66">
+        <v>361.84</v>
+      </c>
+      <c r="E87" s="64">
+        <v>132071.89</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B88">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C88">
+        <is>
+          <t xml:space="preserve">Kab. Sragen</t>
+        </is>
+      </c>
+      <c r="D88" s="66">
+        <v>586.17</v>
+      </c>
+      <c r="E88" s="64">
+        <v>213952.27</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B89">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C89">
+        <is>
+          <t xml:space="preserve">Kab. Blora</t>
+        </is>
+      </c>
+      <c r="D89" s="66">
+        <v>226.85</v>
+      </c>
+      <c r="E89" s="64">
+        <v>82801.58</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B90">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C90">
+        <is>
+          <t xml:space="preserve">Kab. Rembang</t>
+        </is>
+      </c>
+      <c r="D90" s="66">
+        <v>245.66</v>
+      </c>
+      <c r="E90" s="64">
+        <v>89666.36</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B91">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C91">
+        <is>
+          <t xml:space="preserve">Kab. Pati</t>
+        </is>
+      </c>
+      <c r="D91" s="66">
+        <v>662.09</v>
+      </c>
+      <c r="E91" s="64">
+        <v>241664.31</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B92">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C92">
+        <is>
+          <t xml:space="preserve">Kab. Jepara</t>
+        </is>
+      </c>
+      <c r="D92" s="66">
+        <v>400.08</v>
+      </c>
+      <c r="E92" s="64">
+        <v>146028.40</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B93">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C93">
+        <is>
+          <t xml:space="preserve">Kab. Demak</t>
+        </is>
+      </c>
+      <c r="D93" s="66">
+        <v>722.37</v>
+      </c>
+      <c r="E93" s="64">
+        <v>263666.36</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B94">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C94">
+        <is>
+          <t xml:space="preserve">Kab. Semarang</t>
+        </is>
+      </c>
+      <c r="D94" s="66">
+        <v>526.55</v>
+      </c>
+      <c r="E94" s="64">
+        <v>192189.00</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B95">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C95">
+        <is>
+          <t xml:space="preserve">Kab. Temanggung</t>
+        </is>
+      </c>
+      <c r="D95" s="66">
+        <v>500.17</v>
+      </c>
+      <c r="E95" s="64">
+        <v>182562.96</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B96">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C96">
+        <is>
+          <t xml:space="preserve">Kab. Batang</t>
+        </is>
+      </c>
+      <c r="D96" s="66">
+        <v>324.16</v>
+      </c>
+      <c r="E96" s="64">
+        <v>118317.38</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B97">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C97">
+        <is>
+          <t xml:space="preserve">Kab. Pekalongan</t>
+        </is>
+      </c>
+      <c r="D97" s="66">
+        <v>387.53</v>
+      </c>
+      <c r="E97" s="64">
+        <v>141447.87</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B98">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C98">
+        <is>
+          <t xml:space="preserve">Kab. Pemalang</t>
+        </is>
+      </c>
+      <c r="D98" s="66">
+        <v>588.60</v>
+      </c>
+      <c r="E98" s="64">
+        <v>214837.39</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B99">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C99">
+        <is>
+          <t xml:space="preserve">Kab. Tegal</t>
+        </is>
+      </c>
+      <c r="D99" s="66">
+        <v>670.74</v>
+      </c>
+      <c r="E99" s="64">
+        <v>244819.49</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B100">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C100">
+        <is>
+          <t xml:space="preserve">Kab. Brebes</t>
+        </is>
+      </c>
+      <c r="D100" s="66">
+        <v>983.19</v>
+      </c>
+      <c r="E100" s="64">
+        <v>358865.26</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B101">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C101">
+        <is>
+          <t xml:space="preserve">Kota Magelang</t>
+        </is>
+      </c>
+      <c r="D101" s="66">
+        <v>80.68</v>
+      </c>
+      <c r="E101" s="64">
+        <v>29447.93</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B102">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C102">
+        <is>
+          <t xml:space="preserve">Kota Salatiga</t>
+        </is>
+      </c>
+      <c r="D102" s="66">
+        <v>112.24</v>
+      </c>
+      <c r="E102" s="64">
+        <v>40969.24</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B103">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C103">
+        <is>
+          <t xml:space="preserve">Kota Semarang</t>
+        </is>
+      </c>
+      <c r="D103" s="64">
+        <v>1180.14</v>
+      </c>
+      <c r="E103" s="64">
+        <v>430749.75</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B104">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C104">
+        <is>
+          <t xml:space="preserve">Kota Tegal</t>
+        </is>
+      </c>
+      <c r="D104" s="66">
+        <v>201.57</v>
+      </c>
+      <c r="E104" s="64">
+        <v>73573.52</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B105">
+        <is>
+          <t xml:space="preserve">Daerah Istimewa Yogyakarta</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C105">
+        <is>
+          <t xml:space="preserve">Kab. Kulon Progo</t>
+        </is>
+      </c>
+      <c r="D105" s="66">
+        <v>177.14</v>
+      </c>
+      <c r="E105" s="64">
+        <v>64654.35</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B106">
+        <is>
+          <t xml:space="preserve">Daerah Istimewa Yogyakarta</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C106">
+        <is>
+          <t xml:space="preserve">Kab. Sleman</t>
+        </is>
+      </c>
+      <c r="D106" s="66">
+        <v>735.57</v>
+      </c>
+      <c r="E106" s="64">
+        <v>268481.59</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B107">
+        <is>
+          <t xml:space="preserve">Daerah Istimewa Yogyakarta</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C107">
+        <is>
+          <t xml:space="preserve">Kota Yogyakarta</t>
+        </is>
+      </c>
+      <c r="D107" s="66">
+        <v>327.40</v>
+      </c>
+      <c r="E107" s="64">
+        <v>119501.69</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B108">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C108">
+        <is>
+          <t xml:space="preserve">Kab. Pacitan</t>
+        </is>
+      </c>
+      <c r="D108" s="66">
+        <v>286.73</v>
+      </c>
+      <c r="E108" s="64">
+        <v>104654.83</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B109">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C109">
+        <is>
+          <t xml:space="preserve">Kab. Ponorogo</t>
+        </is>
+      </c>
+      <c r="D109" s="66">
+        <v>387.78</v>
+      </c>
+      <c r="E109" s="64">
+        <v>141540.58</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B110">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C110">
+        <is>
+          <t xml:space="preserve">Kab. Trenggalek</t>
+        </is>
+      </c>
+      <c r="D110" s="66">
+        <v>293.96</v>
+      </c>
+      <c r="E110" s="64">
+        <v>107293.65</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B111">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C111">
+        <is>
+          <t xml:space="preserve">Kab. Tulungagung</t>
+        </is>
+      </c>
+      <c r="D111" s="66">
+        <v>548.30</v>
+      </c>
+      <c r="E111" s="64">
+        <v>200127.68</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B112">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C112">
+        <is>
+          <t xml:space="preserve">Kab. Blitar</t>
+        </is>
+      </c>
+      <c r="D112" s="66">
+        <v>409.93</v>
+      </c>
+      <c r="E112" s="64">
+        <v>149623.83</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B113">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C113">
+        <is>
+          <t xml:space="preserve">Kab. Kediri</t>
+        </is>
+      </c>
+      <c r="D113" s="66">
+        <v>533.82</v>
+      </c>
+      <c r="E113" s="64">
+        <v>194845.76</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B114">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C114">
+        <is>
+          <t xml:space="preserve">Kab. Lumajang</t>
+        </is>
+      </c>
+      <c r="D114" s="66">
+        <v>501.50</v>
+      </c>
+      <c r="E114" s="64">
+        <v>183048.96</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B115">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C115">
+        <is>
+          <t xml:space="preserve">Kab. Banyuwangi</t>
+        </is>
+      </c>
+      <c r="D115" s="64">
+        <v>1252.87</v>
+      </c>
+      <c r="E115" s="64">
+        <v>457297.22</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B116">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C116">
+        <is>
+          <t xml:space="preserve">Kab. Situbondo</t>
+        </is>
+      </c>
+      <c r="D116" s="66">
+        <v>257.17</v>
+      </c>
+      <c r="E116" s="64">
+        <v>93865.59</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B117">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C117">
+        <is>
+          <t xml:space="preserve">Kab. Jombang</t>
+        </is>
+      </c>
+      <c r="D117" s="66">
+        <v>530.37</v>
+      </c>
+      <c r="E117" s="64">
+        <v>193583.44</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B118">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C118">
+        <is>
+          <t xml:space="preserve">Kab. Nganjuk</t>
+        </is>
+      </c>
+      <c r="D118" s="66">
+        <v>443.87</v>
+      </c>
+      <c r="E118" s="64">
+        <v>162013.72</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B119">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C119">
+        <is>
+          <t xml:space="preserve">Kab. Magetan</t>
+        </is>
+      </c>
+      <c r="D119" s="66">
+        <v>268.32</v>
+      </c>
+      <c r="E119" s="64">
+        <v>97938.55</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B120">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C120">
+        <is>
+          <t xml:space="preserve">Kab. Ngawi</t>
+        </is>
+      </c>
+      <c r="D120" s="66">
+        <v>356.72</v>
+      </c>
+      <c r="E120" s="64">
+        <v>130204.03</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B121">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C121">
+        <is>
+          <t xml:space="preserve">Kab. Bojonegoro</t>
+        </is>
+      </c>
+      <c r="D121" s="66">
+        <v>536.50</v>
+      </c>
+      <c r="E121" s="64">
+        <v>195823.81</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B122">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C122">
+        <is>
+          <t xml:space="preserve">Kab. Tuban</t>
+        </is>
+      </c>
+      <c r="D122" s="66">
+        <v>503.17</v>
+      </c>
+      <c r="E122" s="64">
+        <v>183655.24</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B123">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C123">
+        <is>
+          <t xml:space="preserve">Kab. Lamongan</t>
+        </is>
+      </c>
+      <c r="D123" s="66">
+        <v>221.94</v>
+      </c>
+      <c r="E123" s="64">
+        <v>81008.10</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B124">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C124">
+        <is>
+          <t xml:space="preserve">Kab. Pamekasan</t>
+        </is>
+      </c>
+      <c r="D124" s="66">
+        <v>276.60</v>
+      </c>
+      <c r="E124" s="64">
+        <v>100957.25</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B125">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C125">
+        <is>
+          <t xml:space="preserve">Kab. Sumenep</t>
+        </is>
+      </c>
+      <c r="D125" s="66">
+        <v>367.44</v>
+      </c>
+      <c r="E125" s="64">
+        <v>134116.61</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B126">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C126">
+        <is>
+          <t xml:space="preserve">Kota Kediri</t>
+        </is>
+      </c>
+      <c r="D126" s="66">
+        <v>169.35</v>
+      </c>
+      <c r="E126" s="64">
+        <v>61812.13</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B127">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C127">
+        <is>
+          <t xml:space="preserve">Kota Blitar</t>
+        </is>
+      </c>
+      <c r="D127" s="66">
+        <v>75.19</v>
+      </c>
+      <c r="E127" s="64">
+        <v>27442.53</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B128">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C128">
+        <is>
+          <t xml:space="preserve">Kota Malang</t>
+        </is>
+      </c>
+      <c r="D128" s="66">
+        <v>677.78</v>
+      </c>
+      <c r="E128" s="64">
+        <v>247388.97</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B129">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C129">
+        <is>
+          <t xml:space="preserve">Kota Probolinggo</t>
+        </is>
+      </c>
+      <c r="D129" s="66">
+        <v>96.57</v>
+      </c>
+      <c r="E129" s="64">
+        <v>35247.76</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B130">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C130">
+        <is>
+          <t xml:space="preserve">Kota Pasuruan</t>
+        </is>
+      </c>
+      <c r="D130" s="66">
+        <v>135.20</v>
+      </c>
+      <c r="E130" s="64">
+        <v>49349.42</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B131">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C131">
+        <is>
+          <t xml:space="preserve">Kota Madiun</t>
+        </is>
+      </c>
+      <c r="D131" s="66">
+        <v>119.71</v>
+      </c>
+      <c r="E131" s="64">
+        <v>43695.25</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B132">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C132">
+        <is>
+          <t xml:space="preserve">Kota Surabaya</t>
+        </is>
+      </c>
+      <c r="D132" s="64">
+        <v>1782.51</v>
+      </c>
+      <c r="E132" s="64">
+        <v>650614.62</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B133">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C133">
+        <is>
+          <t xml:space="preserve">Kota Batu</t>
+        </is>
+      </c>
+      <c r="D133" s="66">
+        <v>114.42</v>
+      </c>
+      <c r="E133" s="64">
+        <v>41762.47</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B134">
+        <is>
+          <t xml:space="preserve">Banten</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C134">
+        <is>
+          <t xml:space="preserve">Kab. Serang</t>
+        </is>
+      </c>
+      <c r="D134" s="64">
+        <v>1163.84</v>
+      </c>
+      <c r="E134" s="64">
+        <v>424801.97</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B135">
+        <is>
+          <t xml:space="preserve">Banten</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C135">
+        <is>
+          <t xml:space="preserve">Kota Cilegon</t>
+        </is>
+      </c>
+      <c r="D135" s="66">
+        <v>217.45</v>
+      </c>
+      <c r="E135" s="64">
+        <v>79368.52</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B136">
+        <is>
+          <t xml:space="preserve">Banten</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C136">
+        <is>
+          <t xml:space="preserve">Kota Tangerang Selatan</t>
+        </is>
+      </c>
+      <c r="D136" s="66">
+        <v>799.07</v>
+      </c>
+      <c r="E136" s="64">
+        <v>291659.27</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B137">
+        <is>
+          <t xml:space="preserve">Bali</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C137">
+        <is>
+          <t xml:space="preserve">Kab. Jembrana</t>
+        </is>
+      </c>
+      <c r="D137" s="66">
+        <v>162.73</v>
+      </c>
+      <c r="E137" s="64">
+        <v>59395.72</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B138">
+        <is>
+          <t xml:space="preserve">Bali</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C138">
+        <is>
+          <t xml:space="preserve">Kab. Tabanan</t>
+        </is>
+      </c>
+      <c r="D138" s="66">
+        <v>230.82</v>
+      </c>
+      <c r="E138" s="64">
+        <v>84247.48</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B139">
+        <is>
+          <t xml:space="preserve">Bali</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C139">
+        <is>
+          <t xml:space="preserve">Kab. Badung</t>
+        </is>
+      </c>
+      <c r="D139" s="66">
+        <v>319.81</v>
+      </c>
+      <c r="E139" s="64">
+        <v>116731.24</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B140">
+        <is>
+          <t xml:space="preserve">Bali</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C140">
+        <is>
+          <t xml:space="preserve">Kab. Gianyar</t>
+        </is>
+      </c>
+      <c r="D140" s="66">
+        <v>387.23</v>
+      </c>
+      <c r="E140" s="64">
+        <v>141337.13</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B141">
+        <is>
+          <t xml:space="preserve">Bali</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C141">
+        <is>
+          <t xml:space="preserve">Kab. Bangli</t>
+        </is>
+      </c>
+      <c r="D141" s="66">
+        <v>110.90</v>
+      </c>
+      <c r="E141" s="64">
+        <v>40479.96</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B142">
+        <is>
+          <t xml:space="preserve">Bali</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C142">
+        <is>
+          <t xml:space="preserve">Kab. Buleleng</t>
+        </is>
+      </c>
+      <c r="D142" s="66">
+        <v>339.10</v>
+      </c>
+      <c r="E142" s="64">
+        <v>123771.50</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B143">
+        <is>
+          <t xml:space="preserve">Bali</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C143">
+        <is>
+          <t xml:space="preserve">Kota Denpasar</t>
+        </is>
+      </c>
+      <c r="D143" s="66">
+        <v>957.59</v>
+      </c>
+      <c r="E143" s="64">
+        <v>349519.44</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B144">
+        <is>
+          <t xml:space="preserve">Nusa Tenggara Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C144">
+        <is>
+          <t xml:space="preserve">Kab. Lombok Timur</t>
+        </is>
+      </c>
+      <c r="D144" s="66">
+        <v>483.44</v>
+      </c>
+      <c r="E144" s="64">
+        <v>176454.72</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B145">
+        <is>
+          <t xml:space="preserve">Nusa Tenggara Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C145">
+        <is>
+          <t xml:space="preserve">Kab. Sumbawa</t>
+        </is>
+      </c>
+      <c r="D145" s="66">
+        <v>259.46</v>
+      </c>
+      <c r="E145" s="64">
+        <v>94704.18</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B146">
+        <is>
+          <t xml:space="preserve">Nusa Tenggara Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C146">
+        <is>
+          <t xml:space="preserve">Kota Mataram</t>
+        </is>
+      </c>
+      <c r="D146" s="66">
+        <v>263.98</v>
+      </c>
+      <c r="E146" s="64">
+        <v>96354.09</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B147">
+        <is>
+          <t xml:space="preserve">Nusa Tenggara Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C147">
+        <is>
+          <t xml:space="preserve">Kab. Alor</t>
+        </is>
+      </c>
+      <c r="D147" s="66">
+        <v>116.53</v>
+      </c>
+      <c r="E147" s="64">
+        <v>42533.30</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B148">
+        <is>
+          <t xml:space="preserve">Nusa Tenggara Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C148">
+        <is>
+          <t xml:space="preserve">Kab. Manggarai Barat</t>
+        </is>
+      </c>
+      <c r="D148" s="66">
+        <v>82.18</v>
+      </c>
+      <c r="E148" s="64">
+        <v>29995.84</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B149">
+        <is>
+          <t xml:space="preserve">Nusa Tenggara Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C149">
+        <is>
+          <t xml:space="preserve">Kota Kupang</t>
+        </is>
+      </c>
+      <c r="D149" s="66">
+        <v>221.38</v>
+      </c>
+      <c r="E149" s="64">
+        <v>80803.34</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B150">
+        <is>
+          <t xml:space="preserve">Kalimantan Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C150">
+        <is>
+          <t xml:space="preserve">Kab. Sambas</t>
+        </is>
+      </c>
+      <c r="D150" s="66">
+        <v>277.38</v>
+      </c>
+      <c r="E150" s="64">
+        <v>101244.25</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B151">
+        <is>
+          <t xml:space="preserve">Kalimantan Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C151">
+        <is>
+          <t xml:space="preserve">Kab. Mempawah</t>
+        </is>
+      </c>
+      <c r="D151" s="66">
+        <v>82.24</v>
+      </c>
+      <c r="E151" s="64">
+        <v>30015.96</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B152">
+        <is>
+          <t xml:space="preserve">Kalimantan Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C152">
+        <is>
+          <t xml:space="preserve">Kab. Sanggau</t>
+        </is>
+      </c>
+      <c r="D152" s="66">
+        <v>242.41</v>
+      </c>
+      <c r="E152" s="64">
+        <v>88479.29</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B153">
+        <is>
+          <t xml:space="preserve">Kalimantan Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C153">
+        <is>
+          <t xml:space="preserve">Kab. Melawi</t>
+        </is>
+      </c>
+      <c r="D153" s="66">
+        <v>83.63</v>
+      </c>
+      <c r="E153" s="64">
+        <v>30524.07</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B154">
+        <is>
+          <t xml:space="preserve">Kalimantan Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C154">
+        <is>
+          <t xml:space="preserve">Kota Pontianak</t>
+        </is>
+      </c>
+      <c r="D154" s="66">
+        <v>396.30</v>
+      </c>
+      <c r="E154" s="64">
+        <v>144651.25</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B155">
+        <is>
+          <t xml:space="preserve">Kalimantan Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C155">
+        <is>
+          <t xml:space="preserve">Kota Singkawang</t>
+        </is>
+      </c>
+      <c r="D155" s="66">
+        <v>117.53</v>
+      </c>
+      <c r="E155" s="64">
+        <v>42899.18</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B156">
+        <is>
+          <t xml:space="preserve">Kalimantan Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C156">
+        <is>
+          <t xml:space="preserve">Kab. Kapuas</t>
+        </is>
+      </c>
+      <c r="D156" s="66">
+        <v>205.20</v>
+      </c>
+      <c r="E156" s="64">
+        <v>74898.00</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B157">
+        <is>
+          <t xml:space="preserve">Kalimantan Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C157">
+        <is>
+          <t xml:space="preserve">Kab. Barito Utara</t>
+        </is>
+      </c>
+      <c r="D157" s="66">
+        <v>63.37</v>
+      </c>
+      <c r="E157" s="64">
+        <v>23129.61</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B158">
+        <is>
+          <t xml:space="preserve">Kalimantan Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C158">
+        <is>
+          <t xml:space="preserve">Kab. Seruyan</t>
+        </is>
+      </c>
+      <c r="D158" s="66">
+        <v>81.46</v>
+      </c>
+      <c r="E158" s="64">
+        <v>29731.08</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B159">
+        <is>
+          <t xml:space="preserve">Kalimantan Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C159">
+        <is>
+          <t xml:space="preserve">Kab. Gunung Mas</t>
+        </is>
+      </c>
+      <c r="D159" s="66">
+        <v>101.55</v>
+      </c>
+      <c r="E159" s="64">
+        <v>37065.75</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B160">
+        <is>
+          <t xml:space="preserve">Kalimantan Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C160">
+        <is>
+          <t xml:space="preserve">Kab. Pulang Pisau</t>
+        </is>
+      </c>
+      <c r="D160" s="66">
+        <v>67.25</v>
+      </c>
+      <c r="E160" s="64">
+        <v>24546.07</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B161">
+        <is>
+          <t xml:space="preserve">Kalimantan Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C161">
+        <is>
+          <t xml:space="preserve">Kab. Barito Timur</t>
+        </is>
+      </c>
+      <c r="D161" s="66">
+        <v>46.51</v>
+      </c>
+      <c r="E161" s="64">
+        <v>16977.76</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B162">
+        <is>
+          <t xml:space="preserve">Kalimantan Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C162">
+        <is>
+          <t xml:space="preserve">Kota Palangkaraya</t>
+        </is>
+      </c>
+      <c r="D162" s="66">
+        <v>147.92</v>
+      </c>
+      <c r="E162" s="64">
+        <v>53990.25</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B163">
+        <is>
+          <t xml:space="preserve">Kalimantan Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C163">
+        <is>
+          <t xml:space="preserve">Kab. Tanah Laut</t>
+        </is>
+      </c>
+      <c r="D163" s="66">
+        <v>141.74</v>
+      </c>
+      <c r="E163" s="64">
+        <v>51733.64</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B164">
+        <is>
+          <t xml:space="preserve">Kalimantan Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C164">
+        <is>
+          <t xml:space="preserve">Kab. Kotabaru</t>
+        </is>
+      </c>
+      <c r="D164" s="66">
+        <v>130.25</v>
+      </c>
+      <c r="E164" s="64">
+        <v>47540.81</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B165">
+        <is>
+          <t xml:space="preserve">Kalimantan Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C165">
+        <is>
+          <t xml:space="preserve">Kab. Banjar</t>
+        </is>
+      </c>
+      <c r="D165" s="66">
+        <v>407.66</v>
+      </c>
+      <c r="E165" s="64">
+        <v>148795.80</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B166">
+        <is>
+          <t xml:space="preserve">Kalimantan Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C166">
+        <is>
+          <t xml:space="preserve">Kab. Barito Kuala</t>
+        </is>
+      </c>
+      <c r="D166" s="66">
+        <v>94.96</v>
+      </c>
+      <c r="E166" s="64">
+        <v>34660.04</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B167">
+        <is>
+          <t xml:space="preserve">Kalimantan Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C167">
+        <is>
+          <t xml:space="preserve">Kab. Tapin</t>
+        </is>
+      </c>
+      <c r="D167" s="66">
+        <v>80.49</v>
+      </c>
+      <c r="E167" s="64">
+        <v>29379.14</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B168">
+        <is>
+          <t xml:space="preserve">Kalimantan Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C168">
+        <is>
+          <t xml:space="preserve">Kab. Hulu Sungai Selatan</t>
+        </is>
+      </c>
+      <c r="D168" s="66">
+        <v>96.01</v>
+      </c>
+      <c r="E168" s="64">
+        <v>35042.92</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B169">
+        <is>
+          <t xml:space="preserve">Kalimantan Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C169">
+        <is>
+          <t xml:space="preserve">Kab. Hulu Sungai Tengah</t>
+        </is>
+      </c>
+      <c r="D169" s="66">
+        <v>103.49</v>
+      </c>
+      <c r="E169" s="64">
+        <v>37773.27</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B170">
+        <is>
+          <t xml:space="preserve">Kalimantan Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C170">
+        <is>
+          <t xml:space="preserve">Kab. Hulu Sungai Utara</t>
+        </is>
+      </c>
+      <c r="D170" s="66">
+        <v>96.66</v>
+      </c>
+      <c r="E170" s="64">
+        <v>35280.75</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B171">
+        <is>
+          <t xml:space="preserve">Kalimantan Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C171">
+        <is>
+          <t xml:space="preserve">Kab. Tabalong</t>
+        </is>
+      </c>
+      <c r="D171" s="66">
+        <v>101.32</v>
+      </c>
+      <c r="E171" s="64">
+        <v>36982.53</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B172">
+        <is>
+          <t xml:space="preserve">Kalimantan Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C172">
+        <is>
+          <t xml:space="preserve">Kab. Tanah Bumbu</t>
+        </is>
+      </c>
+      <c r="D172" s="66">
+        <v>164.35</v>
+      </c>
+      <c r="E172" s="64">
+        <v>59986.29</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B173">
+        <is>
+          <t xml:space="preserve">Kalimantan Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C173">
+        <is>
+          <t xml:space="preserve">Kab. Balangan</t>
+        </is>
+      </c>
+      <c r="D173" s="66">
+        <v>56.00</v>
+      </c>
+      <c r="E173" s="64">
+        <v>20440.98</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B174">
+        <is>
+          <t xml:space="preserve">Kalimantan Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C174">
+        <is>
+          <t xml:space="preserve">Kota Banjarmasin</t>
+        </is>
+      </c>
+      <c r="D174" s="66">
+        <v>506.45</v>
+      </c>
+      <c r="E174" s="64">
+        <v>184856.04</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B175">
+        <is>
+          <t xml:space="preserve">Kalimantan Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C175">
+        <is>
+          <t xml:space="preserve">Kota Banjarbaru</t>
+        </is>
+      </c>
+      <c r="D175" s="66">
+        <v>164.71</v>
+      </c>
+      <c r="E175" s="64">
+        <v>60120.18</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B176">
+        <is>
+          <t xml:space="preserve">Kalimantan Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C176">
+        <is>
+          <t xml:space="preserve">Kab. Paser</t>
+        </is>
+      </c>
+      <c r="D176" s="66">
+        <v>115.29</v>
+      </c>
+      <c r="E176" s="64">
+        <v>42080.85</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B177">
+        <is>
+          <t xml:space="preserve">Kalimantan Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C177">
+        <is>
+          <t xml:space="preserve">Kab. Kutai Kartanegara</t>
+        </is>
+      </c>
+      <c r="D177" s="66">
+        <v>222.59</v>
+      </c>
+      <c r="E177" s="64">
+        <v>81243.53</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B178">
+        <is>
+          <t xml:space="preserve">Kalimantan Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C178">
+        <is>
+          <t xml:space="preserve">Kab. Kutai Timur</t>
+        </is>
+      </c>
+      <c r="D178" s="66">
+        <v>212.22</v>
+      </c>
+      <c r="E178" s="64">
+        <v>77461.58</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B179">
+        <is>
+          <t xml:space="preserve">Kalimantan Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C179">
+        <is>
+          <t xml:space="preserve">Kab. Penajam Paser Utara</t>
+        </is>
+      </c>
+      <c r="D179" s="66">
+        <v>92.51</v>
+      </c>
+      <c r="E179" s="64">
+        <v>33766.52</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B180">
+        <is>
+          <t xml:space="preserve">Kalimantan Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C180">
+        <is>
+          <t xml:space="preserve">Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="D180" s="66">
+        <v>497.21</v>
+      </c>
+      <c r="E180" s="64">
+        <v>181479.86</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B181">
+        <is>
+          <t xml:space="preserve">Kalimantan Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C181">
+        <is>
+          <t xml:space="preserve">Kota Samarinda</t>
+        </is>
+      </c>
+      <c r="D181" s="66">
+        <v>581.85</v>
+      </c>
+      <c r="E181" s="64">
+        <v>212376.71</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B182">
+        <is>
+          <t xml:space="preserve">Kalimantan Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C182">
+        <is>
+          <t xml:space="preserve">Kota Bontang</t>
+        </is>
+      </c>
+      <c r="D182" s="66">
+        <v>103.82</v>
+      </c>
+      <c r="E182" s="64">
+        <v>37894.33</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B183">
+        <is>
+          <t xml:space="preserve">Kalimantan Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C183">
+        <is>
+          <t xml:space="preserve">Kab. Nunukan</t>
+        </is>
+      </c>
+      <c r="D183" s="66">
+        <v>41.81</v>
+      </c>
+      <c r="E183" s="64">
+        <v>15260.25</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B184">
+        <is>
+          <t xml:space="preserve">Kalimantan Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C184">
+        <is>
+          <t xml:space="preserve">Kab. Tana Tidung</t>
+        </is>
+      </c>
+      <c r="D184" s="66">
+        <v>13.24</v>
+      </c>
+      <c r="E184" s="64">
+        <v>4832.89</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B185">
+        <is>
+          <t xml:space="preserve">Sulawesi Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C185">
+        <is>
+          <t xml:space="preserve">Kab. Kepulauan Sangihe</t>
+        </is>
+      </c>
+      <c r="D185" s="66">
+        <v>55.70</v>
+      </c>
+      <c r="E185" s="64">
+        <v>20332.25</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B186">
+        <is>
+          <t xml:space="preserve">Sulawesi Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C186">
+        <is>
+          <t xml:space="preserve">Kab. Minahasa Selatan</t>
+        </is>
+      </c>
+      <c r="D186" s="66">
+        <v>94.59</v>
+      </c>
+      <c r="E186" s="64">
+        <v>34523.60</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B187">
+        <is>
+          <t xml:space="preserve">Sulawesi Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C187">
+        <is>
+          <t xml:space="preserve">Kab. Minahasa Tenggara</t>
+        </is>
+      </c>
+      <c r="D187" s="66">
+        <v>45.37</v>
+      </c>
+      <c r="E187" s="64">
+        <v>16559.47</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B188">
+        <is>
+          <t xml:space="preserve">Sulawesi Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C188">
+        <is>
+          <t xml:space="preserve">Kab. Bolaang Mongondow Utara</t>
+        </is>
+      </c>
+      <c r="D188" s="66">
+        <v>41.56</v>
+      </c>
+      <c r="E188" s="64">
+        <v>15167.94</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B189">
+        <is>
+          <t xml:space="preserve">Sulawesi Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C189">
+        <is>
+          <t xml:space="preserve">Kab. Bolaang Mongondow Selatan</t>
+        </is>
+      </c>
+      <c r="D189" s="66">
+        <v>34.90</v>
+      </c>
+      <c r="E189" s="64">
+        <v>12736.86</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B190">
+        <is>
+          <t xml:space="preserve">Sulawesi Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C190">
+        <is>
+          <t xml:space="preserve">Kota Manado</t>
+        </is>
+      </c>
+      <c r="D190" s="66">
+        <v>339.89</v>
+      </c>
+      <c r="E190" s="64">
+        <v>124059.81</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B191">
+        <is>
+          <t xml:space="preserve">Sulawesi Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C191">
+        <is>
+          <t xml:space="preserve">Kota Bitung</t>
+        </is>
+      </c>
+      <c r="D191" s="66">
+        <v>158.56</v>
+      </c>
+      <c r="E191" s="64">
+        <v>57874.58</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B192">
+        <is>
+          <t xml:space="preserve">Sulawesi Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C192">
+        <is>
+          <t xml:space="preserve">Kota Kotamobagu</t>
+        </is>
+      </c>
+      <c r="D192" s="66">
+        <v>86.63</v>
+      </c>
+      <c r="E192" s="64">
+        <v>31620.68</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B193">
+        <is>
+          <t xml:space="preserve">Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C193">
+        <is>
+          <t xml:space="preserve">Kab. Donggala</t>
+        </is>
+      </c>
+      <c r="D193" s="66">
+        <v>121.64</v>
+      </c>
+      <c r="E193" s="64">
+        <v>44400.06</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B194">
+        <is>
+          <t xml:space="preserve">Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C194">
+        <is>
+          <t xml:space="preserve">Kab. Parigi Moutong</t>
+        </is>
+      </c>
+      <c r="D194" s="66">
+        <v>225.59</v>
+      </c>
+      <c r="E194" s="64">
+        <v>82341.99</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B195">
+        <is>
+          <t xml:space="preserve">Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C195">
+        <is>
+          <t xml:space="preserve">Kab. Sigi</t>
+        </is>
+      </c>
+      <c r="D195" s="66">
+        <v>128.79</v>
+      </c>
+      <c r="E195" s="64">
+        <v>47008.35</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B196">
+        <is>
+          <t xml:space="preserve">Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C196">
+        <is>
+          <t xml:space="preserve">Kab. Banggai Laut</t>
+        </is>
+      </c>
+      <c r="D196" s="66">
+        <v>35.44</v>
+      </c>
+      <c r="E196" s="64">
+        <v>12933.78</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B197">
+        <is>
+          <t xml:space="preserve">Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C197">
+        <is>
+          <t xml:space="preserve">Kota Palu</t>
+        </is>
+      </c>
+      <c r="D197" s="66">
+        <v>186.93</v>
+      </c>
+      <c r="E197" s="64">
+        <v>68228.90</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B198">
+        <is>
+          <t xml:space="preserve">Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C198">
+        <is>
+          <t xml:space="preserve">Kab. Kepulauan Selayar</t>
+        </is>
+      </c>
+      <c r="D198" s="66">
+        <v>56.13</v>
+      </c>
+      <c r="E198" s="64">
+        <v>20488.47</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B199">
+        <is>
+          <t xml:space="preserve">Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C199">
+        <is>
+          <t xml:space="preserve">Kab. Bulukumba</t>
+        </is>
+      </c>
+      <c r="D199" s="66">
+        <v>173.94</v>
+      </c>
+      <c r="E199" s="64">
+        <v>63488.39</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B200">
+        <is>
+          <t xml:space="preserve">Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C200">
+        <is>
+          <t xml:space="preserve">Kab. Bantaeng</t>
+        </is>
+      </c>
+      <c r="D200" s="66">
+        <v>80.68</v>
+      </c>
+      <c r="E200" s="64">
+        <v>29446.45</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B201">
+        <is>
+          <t xml:space="preserve">Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C201">
+        <is>
+          <t xml:space="preserve">Kab. Jeneponto</t>
+        </is>
+      </c>
+      <c r="D201" s="66">
+        <v>160.64</v>
+      </c>
+      <c r="E201" s="64">
+        <v>58635.06</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B202">
+        <is>
+          <t xml:space="preserve">Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C202">
+        <is>
+          <t xml:space="preserve">Kab. Sinjai</t>
+        </is>
+      </c>
+      <c r="D202" s="66">
+        <v>108.31</v>
+      </c>
+      <c r="E202" s="64">
+        <v>39534.76</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B203">
+        <is>
+          <t xml:space="preserve">Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C203">
+        <is>
+          <t xml:space="preserve">Kab. Bone</t>
+        </is>
+      </c>
+      <c r="D203" s="66">
+        <v>403.38</v>
+      </c>
+      <c r="E203" s="64">
+        <v>147231.88</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B204">
+        <is>
+          <t xml:space="preserve">Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C204">
+        <is>
+          <t xml:space="preserve">Kab. Maros</t>
+        </is>
+      </c>
+      <c r="D204" s="66">
+        <v>158.77</v>
+      </c>
+      <c r="E204" s="64">
+        <v>57950.90</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B205">
+        <is>
+          <t xml:space="preserve">Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C205">
+        <is>
+          <t xml:space="preserve">Kab. Pangkajene dan Kepulauan</t>
+        </is>
+      </c>
+      <c r="D205" s="66">
+        <v>138.31</v>
+      </c>
+      <c r="E205" s="64">
+        <v>50483.15</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B206">
+        <is>
+          <t xml:space="preserve">Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C206">
+        <is>
+          <t xml:space="preserve">Kab. Barru</t>
+        </is>
+      </c>
+      <c r="D206" s="66">
+        <v>75.95</v>
+      </c>
+      <c r="E206" s="64">
+        <v>27722.04</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B207">
+        <is>
+          <t xml:space="preserve">Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C207">
+        <is>
+          <t xml:space="preserve">Kab. Soppeng</t>
+        </is>
+      </c>
+      <c r="D207" s="66">
+        <v>95.09</v>
+      </c>
+      <c r="E207" s="64">
+        <v>34707.12</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B208">
+        <is>
+          <t xml:space="preserve">Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C208">
+        <is>
+          <t xml:space="preserve">Kab. Wajo</t>
+        </is>
+      </c>
+      <c r="D208" s="66">
+        <v>151.64</v>
+      </c>
+      <c r="E208" s="64">
+        <v>55348.60</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B209">
+        <is>
+          <t xml:space="preserve">Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C209">
+        <is>
+          <t xml:space="preserve">Kab. Sidenreng Rappang</t>
+        </is>
+      </c>
+      <c r="D209" s="66">
+        <v>128.00</v>
+      </c>
+      <c r="E209" s="64">
+        <v>46718.54</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B210">
+        <is>
+          <t xml:space="preserve">Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C210">
+        <is>
+          <t xml:space="preserve">Kab. Pinrang</t>
+        </is>
+      </c>
+      <c r="D210" s="66">
+        <v>176.90</v>
+      </c>
+      <c r="E210" s="64">
+        <v>64570.25</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B211">
+        <is>
+          <t xml:space="preserve">Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C211">
+        <is>
+          <t xml:space="preserve">Kab. Enrekang</t>
+        </is>
+      </c>
+      <c r="D211" s="66">
+        <v>113.96</v>
+      </c>
+      <c r="E211" s="64">
+        <v>41596.68</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B212">
+        <is>
+          <t xml:space="preserve">Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C212">
+        <is>
+          <t xml:space="preserve">Kab. Luwu Timur</t>
+        </is>
+      </c>
+      <c r="D212" s="66">
+        <v>120.20</v>
+      </c>
+      <c r="E212" s="64">
+        <v>43874.61</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B213">
+        <is>
+          <t xml:space="preserve">Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C213">
+        <is>
+          <t xml:space="preserve">Kota Makassar</t>
+        </is>
+      </c>
+      <c r="D213" s="64">
+        <v>1023.71</v>
+      </c>
+      <c r="E213" s="64">
+        <v>373653.93</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B214">
+        <is>
+          <t xml:space="preserve">Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C214">
+        <is>
+          <t xml:space="preserve">Kota Parepare</t>
+        </is>
+      </c>
+      <c r="D214" s="66">
+        <v>76.25</v>
+      </c>
+      <c r="E214" s="64">
+        <v>27832.35</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B215">
+        <is>
+          <t xml:space="preserve">Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C215">
+        <is>
+          <t xml:space="preserve">Kota Palopo</t>
+        </is>
+      </c>
+      <c r="D215" s="66">
+        <v>92.34</v>
+      </c>
+      <c r="E215" s="64">
+        <v>33704.28</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B216">
+        <is>
+          <t xml:space="preserve">Sulawesi Tenggara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C216">
+        <is>
+          <t xml:space="preserve">Kab. Wakatobi</t>
+        </is>
+      </c>
+      <c r="D216" s="66">
+        <v>79.19</v>
+      </c>
+      <c r="E216" s="64">
+        <v>28902.67</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B217">
+        <is>
+          <t xml:space="preserve">Sulawesi Tenggara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C217">
+        <is>
+          <t xml:space="preserve">Kota Kendari</t>
+        </is>
+      </c>
+      <c r="D217" s="66">
+        <v>264.50</v>
+      </c>
+      <c r="E217" s="64">
+        <v>96542.67</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B218">
+        <is>
+          <t xml:space="preserve">Gorontalo</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C218">
+        <is>
+          <t xml:space="preserve">Kota Gorontalo</t>
+        </is>
+      </c>
+      <c r="D218" s="66">
+        <v>141.21</v>
+      </c>
+      <c r="E218" s="64">
+        <v>51541.50</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B219">
+        <is>
+          <t xml:space="preserve">Sulawesi Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C219">
+        <is>
+          <t xml:space="preserve">Kab. Majene</t>
+        </is>
+      </c>
+      <c r="D219" s="66">
+        <v>69.76</v>
+      </c>
+      <c r="E219" s="64">
+        <v>25463.42</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B220">
+        <is>
+          <t xml:space="preserve">Sulawesi Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C220">
+        <is>
+          <t xml:space="preserve">Kab. Mamuju Tengah</t>
+        </is>
+      </c>
+      <c r="D220" s="66">
+        <v>62.64</v>
+      </c>
+      <c r="E220" s="64">
+        <v>22864.48</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B221">
+        <is>
+          <t xml:space="preserve">Maluku</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C221">
+        <is>
+          <t xml:space="preserve">Kab. Maluku Tengah</t>
+        </is>
+      </c>
+      <c r="D221" s="66">
+        <v>170.32</v>
+      </c>
+      <c r="E221" s="64">
+        <v>62165.92</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B222">
+        <is>
+          <t xml:space="preserve">Maluku</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C222">
+        <is>
+          <t xml:space="preserve">Kab. Buru Selatan</t>
+        </is>
+      </c>
+      <c r="D222" s="66">
+        <v>30.95</v>
+      </c>
+      <c r="E222" s="64">
+        <v>11296.60</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B223">
+        <is>
+          <t xml:space="preserve">Maluku</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C223">
+        <is>
+          <t xml:space="preserve">Kota Tual</t>
+        </is>
+      </c>
+      <c r="D223" s="66">
+        <v>53.73</v>
+      </c>
+      <c r="E223" s="64">
+        <v>19611.92</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B224">
+        <is>
+          <t xml:space="preserve">Maluku Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C224">
+        <is>
+          <t xml:space="preserve">Kota Tidore Kepulauan</t>
+        </is>
+      </c>
+      <c r="D224" s="66">
+        <v>46.12</v>
+      </c>
+      <c r="E224" s="64">
+        <v>16834.53</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B225">
+        <is>
+          <t xml:space="preserve">Papua</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C225">
+        <is>
+          <t xml:space="preserve">Kab. Jayapura</t>
+        </is>
+      </c>
+      <c r="D225" s="66">
+        <v>84.24</v>
+      </c>
+      <c r="E225" s="64">
+        <v>30746.87</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B226">
+        <is>
+          <t xml:space="preserve">Papua</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C226">
+        <is>
+          <t xml:space="preserve">Kab. Biak Numfor</t>
+        </is>
+      </c>
+      <c r="D226" s="66">
+        <v>58.42</v>
+      </c>
+      <c r="E226" s="64">
+        <v>21323.59</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B227">
+        <is>
+          <t xml:space="preserve">Papua</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C227">
+        <is>
+          <t xml:space="preserve">Kab. Keerom</t>
+        </is>
+      </c>
+      <c r="D227" s="66">
+        <v>26.13</v>
+      </c>
+      <c r="E227" s="64">
+        <v>9536.28</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B228">
+        <is>
+          <t xml:space="preserve">Papua</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C228">
+        <is>
+          <t xml:space="preserve">Kota Jayapura</t>
+        </is>
+      </c>
+      <c r="D228" s="66">
+        <v>217.80</v>
+      </c>
+      <c r="E228" s="64">
+        <v>79496.56</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B229">
+        <is>
+          <t xml:space="preserve">Papua Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C229">
+        <is>
+          <t xml:space="preserve">Kab. Manokwari</t>
+        </is>
+      </c>
+      <c r="D229" s="66">
+        <v>160.02</v>
+      </c>
+      <c r="E229" s="64">
+        <v>58405.66</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B230">
+        <is>
+          <t xml:space="preserve">Papua Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C230">
+        <is>
+          <t xml:space="preserve">Kab. Asmat</t>
+        </is>
+      </c>
+      <c r="D230" s="66">
+        <v>44.65</v>
+      </c>
+      <c r="E230" s="64">
+        <v>16298.27</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B231">
+        <is>
+          <t xml:space="preserve">Papua Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C231">
+        <is>
+          <t xml:space="preserve">Kab. Nabire</t>
+        </is>
+      </c>
+      <c r="D231" s="66">
+        <v>67.65</v>
+      </c>
+      <c r="E231" s="64">
+        <v>24693.86</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B232">
+        <is>
+          <t xml:space="preserve">Papua Pegunungan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C232">
+        <is>
+          <t xml:space="preserve">Kab. Lanny Jaya</t>
+        </is>
+      </c>
+      <c r="D232" s="66">
+        <v>80.78</v>
+      </c>
+      <c r="E232" s="64">
+        <v>29483.24</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B233">
+        <is>
+          <t xml:space="preserve">Papua Barat Daya</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C233">
+        <is>
+          <t xml:space="preserve">Kab. Sorong Selatan</t>
+        </is>
+      </c>
+      <c r="D233" s="66">
+        <v>22.38</v>
+      </c>
+      <c r="E233" s="64">
+        <v>8167.39</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B234">
+        <is>
+          <t xml:space="preserve">Papua Barat Daya</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C234">
+        <is>
+          <t xml:space="preserve">Kab. Tambrauw</t>
+        </is>
+      </c>
+      <c r="D234" s="66">
+        <v>11.35</v>
+      </c>
+      <c r="E234" s="64">
+        <v>4143.33</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
